--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="167">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -541,14 +541,6 @@
   </si>
   <si>
     <t>功能清單之通知模組需使用n8n實作尚未完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>設計師休假日尚未校正成存入星期幾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有的創建語法都須返回新id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1738,7 +1730,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1746,16 +1738,6 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>168</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -9,12 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17220" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17220" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="主架構" sheetId="1" r:id="rId1"/>
     <sheet name="功能清單" sheetId="2" r:id="rId2"/>
     <sheet name="開發日誌" sheetId="3" r:id="rId3"/>
+    <sheet name="用戶須提供資料" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="182">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -542,6 +543,58 @@
   <si>
     <t>功能清單之通知模組需使用n8n實作尚未完成</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChannelId</t>
+  </si>
+  <si>
+    <t>ChannelSecret</t>
+  </si>
+  <si>
+    <t>RedirectUri</t>
+  </si>
+  <si>
+    <t>基本資料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料庫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConnectionStrings</t>
+  </si>
+  <si>
+    <t>appsettings.json</t>
+  </si>
+  <si>
+    <t>Line官方帳號登入服務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line官方帳號訊息服務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Channel access token</t>
+  </si>
+  <si>
+    <t>Gmail郵件服務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gmail 應用程式密碼</t>
+  </si>
+  <si>
+    <t>IEmailVerificationService</t>
   </si>
 </sst>
 </file>
@@ -1742,4 +1795,99 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="261" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+</worksheet>
 </file>
--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="188">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -595,6 +595,29 @@
   </si>
   <si>
     <t>IEmailVerificationService</t>
+  </si>
+  <si>
+    <t>訂單取消時限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>My</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>Banner(高清橫向橫幅)3張</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主題廣告(正方形照片)3張</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新聞資訊(垂直照片)3張</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1799,11 +1822,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1818,70 +1841,102 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>172</v>
-      </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>175</v>
-      </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>178</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B12" t="s">
         <v>179</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C12" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>180</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C13" t="s">
         <v>181</v>
       </c>
     </row>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -15,7 +15,8 @@
     <sheet name="主架構" sheetId="1" r:id="rId1"/>
     <sheet name="功能清單" sheetId="2" r:id="rId2"/>
     <sheet name="開發日誌" sheetId="3" r:id="rId3"/>
-    <sheet name="用戶須提供資料" sheetId="4" r:id="rId4"/>
+    <sheet name="管理表單須過" sheetId="5" r:id="rId4"/>
+    <sheet name="用戶須提供資料" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="199">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -617,6 +618,49 @@
   </si>
   <si>
     <t>新聞資訊(垂直照片)3張</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文字風格調整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前端篩選</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>訊息區塊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文化資料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用者權限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能完整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作/頁面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UserManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1822,6 +1866,74 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="261" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="206">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -650,6 +650,33 @@
   </si>
   <si>
     <t>UserManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>標籤使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NewsManagement</t>
   </si>
   <si>
     <t>v</t>
@@ -1866,63 +1893,106 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>194</v>
       </c>
       <c r="B1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>188</v>
       </c>
       <c r="B2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>189</v>
       </c>
       <c r="B3" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>190</v>
       </c>
       <c r="B4" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>191</v>
       </c>
       <c r="B5" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>193</v>
       </c>
       <c r="B6" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>192</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>197</v>
+      </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="226">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -688,6 +688,83 @@
   </si>
   <si>
     <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PortfolioManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格不可換行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProductManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ManageReservation</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>發送通知邏輯尚未完成</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1893,10 +1970,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>194</v>
       </c>
@@ -1906,8 +1983,17 @@
       <c r="C1" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>188</v>
       </c>
@@ -1917,8 +2003,17 @@
       <c r="C2" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>189</v>
       </c>
@@ -1928,8 +2023,17 @@
       <c r="C3" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>190</v>
       </c>
@@ -1939,8 +2043,17 @@
       <c r="C4" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>191</v>
       </c>
@@ -1950,8 +2063,17 @@
       <c r="C5" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>193</v>
       </c>
@@ -1961,8 +2083,17 @@
       <c r="C6" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>200</v>
       </c>
@@ -1972,27 +2103,76 @@
       <c r="C7" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="D7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>192</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>197</v>
-      </c>
-      <c r="C9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B10" t="s">
-        <v>201</v>
       </c>
       <c r="C10" t="s">
         <v>201</v>
+      </c>
+      <c r="D10" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F10" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F12" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="225">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -761,10 +761,6 @@
   </si>
   <si>
     <t>備註</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>發送通知邏輯尚未完成</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2171,9 +2167,6 @@
       <c r="A12" t="s">
         <v>224</v>
       </c>
-      <c r="F12" t="s">
-        <v>225</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17220" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26760" windowHeight="7800" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="主架構" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="233">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -761,6 +761,36 @@
   </si>
   <si>
     <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PGManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DesignerManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1966,10 +1996,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>194</v>
       </c>
@@ -1988,8 +2018,14 @@
       <c r="F1" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>188</v>
       </c>
@@ -2008,8 +2044,14 @@
       <c r="F2" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>189</v>
       </c>
@@ -2028,8 +2070,14 @@
       <c r="F3" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>190</v>
       </c>
@@ -2048,8 +2096,14 @@
       <c r="F4" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>228</v>
+      </c>
+      <c r="H4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>191</v>
       </c>
@@ -2068,8 +2122,14 @@
       <c r="F5" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>193</v>
       </c>
@@ -2088,8 +2148,14 @@
       <c r="F6" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>200</v>
       </c>
@@ -2108,8 +2174,14 @@
       <c r="F7" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>226</v>
+      </c>
+      <c r="H7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>208</v>
       </c>
@@ -2122,8 +2194,14 @@
       <c r="F8" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>226</v>
+      </c>
+      <c r="H8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>192</v>
       </c>
@@ -2142,8 +2220,14 @@
       <c r="F10" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>226</v>
+      </c>
+      <c r="H10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>199</v>
       </c>
@@ -2162,8 +2246,14 @@
       <c r="F11" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>228</v>
+      </c>
+      <c r="H11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>224</v>
       </c>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -9,14 +9,15 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26760" windowHeight="7800" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26085" windowHeight="7800" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="主架構" sheetId="1" r:id="rId1"/>
     <sheet name="功能清單" sheetId="2" r:id="rId2"/>
     <sheet name="開發日誌" sheetId="3" r:id="rId3"/>
     <sheet name="管理表單須過" sheetId="5" r:id="rId4"/>
-    <sheet name="用戶須提供資料" sheetId="4" r:id="rId5"/>
+    <sheet name="代辦清單" sheetId="6" r:id="rId5"/>
+    <sheet name="用戶須提供資料" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="248">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -791,6 +792,62 @@
   </si>
   <si>
     <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CouponPointManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DesignerShiftManagement</t>
+  </si>
+  <si>
+    <t>Report</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MyCoupons</t>
+  </si>
+  <si>
+    <t>優惠券管理少了備註欄為</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的優惠券頁面1.分業系統2.顯示資訊確認</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1996,10 +2053,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>194</v>
       </c>
@@ -2024,8 +2081,20 @@
       <c r="H1" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" t="s">
+        <v>239</v>
+      </c>
+      <c r="L1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>188</v>
       </c>
@@ -2050,8 +2119,17 @@
       <c r="H2" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>234</v>
+      </c>
+      <c r="J2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>189</v>
       </c>
@@ -2076,8 +2154,17 @@
       <c r="H3" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>190</v>
       </c>
@@ -2102,8 +2189,17 @@
       <c r="H4" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>234</v>
+      </c>
+      <c r="J4" t="s">
+        <v>197</v>
+      </c>
+      <c r="K4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>191</v>
       </c>
@@ -2128,8 +2224,17 @@
       <c r="H5" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>193</v>
       </c>
@@ -2154,8 +2259,17 @@
       <c r="H6" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>236</v>
+      </c>
+      <c r="J6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>200</v>
       </c>
@@ -2180,8 +2294,17 @@
       <c r="H7" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>234</v>
+      </c>
+      <c r="J7" t="s">
+        <v>209</v>
+      </c>
+      <c r="K7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>208</v>
       </c>
@@ -2200,8 +2323,14 @@
       <c r="H8" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>234</v>
+      </c>
+      <c r="J8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>192</v>
       </c>
@@ -2226,8 +2355,17 @@
       <c r="H10" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>237</v>
+      </c>
+      <c r="J10" t="s">
+        <v>209</v>
+      </c>
+      <c r="K10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>199</v>
       </c>
@@ -2252,8 +2390,17 @@
       <c r="H11" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" t="s">
+        <v>197</v>
+      </c>
+      <c r="K11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>224</v>
       </c>
@@ -2266,6 +2413,27 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26085" windowHeight="7800" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26085" windowHeight="7800" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="主架構" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="251">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -843,11 +843,23 @@
     <t>MyCoupons</t>
   </si>
   <si>
-    <t>優惠券管理少了備註欄為</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我的優惠券頁面1.分業系統2.顯示資訊確認</t>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2128,6 +2140,9 @@
       <c r="K2" t="s">
         <v>240</v>
       </c>
+      <c r="L2" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -2163,6 +2178,9 @@
       <c r="K3" t="s">
         <v>241</v>
       </c>
+      <c r="L3" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -2198,6 +2216,9 @@
       <c r="K4" t="s">
         <v>242</v>
       </c>
+      <c r="L4" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -2233,6 +2254,9 @@
       <c r="K5" t="s">
         <v>243</v>
       </c>
+      <c r="L5" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -2268,6 +2292,9 @@
       <c r="K6" t="s">
         <v>244</v>
       </c>
+      <c r="L6" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -2303,6 +2330,9 @@
       <c r="K7" t="s">
         <v>241</v>
       </c>
+      <c r="L7" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -2328,6 +2358,9 @@
       </c>
       <c r="J8" t="s">
         <v>197</v>
+      </c>
+      <c r="L8" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -2414,20 +2447,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26085" windowHeight="7800" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26085" windowHeight="7800" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="主架構" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="252">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -860,6 +860,10 @@
   </si>
   <si>
     <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新聞增加連結功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2449,7 +2453,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="256">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -864,6 +864,21 @@
   </si>
   <si>
     <t>新聞增加連結功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;a class="dropdown-item" asp-page="/about"&gt;&lt;i class="far fa-address-card nav-icon icon-width"&gt;&lt;/i&gt; 關於我們&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a class="dropdown-item" asp-page="/Product"&gt;&lt;i class="fab fa-instagram nav-icon icon-width"&gt;&lt;/i&gt; 作品集&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;a class="dropdown-item" asp-page="/MakeReservation"&gt;&lt;i class="fas fa-clipboard-list nav-icon icon-width"&gt;&lt;/i&gt; 所有課程&amp;服務&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;a class="dropdown-item" asp-page="/contact"&gt;&lt;i class="far fa-comment-dots nav-icon icon-width"&gt;&lt;/i&gt; 聯絡我們&lt;/a&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2451,12 +2466,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26085" windowHeight="7800" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26085" windowHeight="7800" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="主架構" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,8 @@
     <sheet name="開發日誌" sheetId="3" r:id="rId3"/>
     <sheet name="管理表單須過" sheetId="5" r:id="rId4"/>
     <sheet name="代辦清單" sheetId="6" r:id="rId5"/>
-    <sheet name="用戶須提供資料" sheetId="4" r:id="rId6"/>
+    <sheet name="架設歷程" sheetId="7" r:id="rId6"/>
+    <sheet name="用戶須提供資料" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="258">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -879,6 +880,14 @@
   </si>
   <si>
     <t>&lt;a class="dropdown-item" asp-page="/contact"&gt;&lt;i class="far fa-comment-dots nav-icon icon-width"&gt;&lt;/i&gt; 聯絡我們&lt;/a&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前mssql已經轉到docker裡面了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在還連不上網站</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2502,6 +2511,30 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="132.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>

--- a/架構文檔.xlsx
+++ b/架構文檔.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26085" windowHeight="7800" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26085" windowHeight="7800" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="主架構" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="279">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -557,25 +557,377 @@
     <t>RedirectUri</t>
   </si>
   <si>
+    <t>ConnectionStrings</t>
+  </si>
+  <si>
+    <t>appsettings.json</t>
+  </si>
+  <si>
+    <t>Channel access token</t>
+  </si>
+  <si>
+    <t>Gmail 應用程式密碼</t>
+  </si>
+  <si>
+    <t>IEmailVerificationService</t>
+  </si>
+  <si>
+    <t>文字風格調整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前端篩選</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>訊息區塊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文化資料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用者權限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能完整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作/頁面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UserManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>標籤使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NewsManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PortfolioManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格不可換行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProductManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ManageReservation</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PGManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DesignerManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CouponPointManagement</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DesignerShiftManagement</t>
+  </si>
+  <si>
+    <t>Report</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MyCoupons</t>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前mssql已經轉到docker裡面了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>照片</t>
+  </si>
+  <si>
+    <t>Banner3-5張</t>
+  </si>
+  <si>
+    <t>新聞照片2-5張</t>
+  </si>
+  <si>
+    <t>新聞內容</t>
+  </si>
+  <si>
+    <t>作品集照片2-5張</t>
+  </si>
+  <si>
+    <t>Logo</t>
+  </si>
+  <si>
+    <t>公司全名</t>
+  </si>
+  <si>
+    <t>公司簡稱</t>
+  </si>
+  <si>
+    <t>聯絡電話</t>
+  </si>
+  <si>
+    <t>電子信箱</t>
+  </si>
+  <si>
+    <t>Facebook 連結</t>
+  </si>
+  <si>
+    <t>Instagram 連結</t>
+  </si>
+  <si>
+    <t>YouTube 連結</t>
+  </si>
+  <si>
+    <t>TikTok 連結</t>
+  </si>
+  <si>
+    <t>可取消時間限制（小時）</t>
+  </si>
+  <si>
     <t>基本資料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line官方帳號</t>
+  </si>
+  <si>
+    <t>預約設定</t>
+  </si>
+  <si>
+    <t>my</t>
+  </si>
+  <si>
+    <t>my、appsettings.json</t>
+  </si>
+  <si>
+    <t>\wwwroot\dist\img</t>
   </si>
   <si>
     <t>資料庫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ConnectionStrings</t>
-  </si>
-  <si>
-    <t>appsettings.json</t>
+  </si>
+  <si>
+    <t>n8n</t>
   </si>
   <si>
     <t>Line官方帳號登入服務</t>
+  </si>
+  <si>
+    <t>Gmail郵件服務</t>
+  </si>
+  <si>
+    <t>信箱</t>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顯示於首頁新聞，日後可更新與新增其他新聞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顯示於作品集，日後可更新與新增其他作品集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司Logo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高畫質，顯示於首頁橫幅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>官方帳號的id，@開頭例如@1234567</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>官方帳號的網址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line官方帳號網址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line官方帳號ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -583,311 +935,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Channel access token</t>
-  </si>
-  <si>
-    <t>Gmail郵件服務</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>信箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gmail 應用程式密碼</t>
-  </si>
-  <si>
-    <t>IEmailVerificationService</t>
-  </si>
-  <si>
-    <t>訂單取消時限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>My</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>Banner(高清橫向橫幅)3張</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主題廣告(正方形照片)3張</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新聞資訊(垂直照片)3張</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文字風格調整</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>前端篩選</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>訊息區塊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中文化資料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用者權限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>功能完整</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作/頁面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UserManagement</t>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>功能正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>標籤使用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NewsManagement</t>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PortfolioManagement</t>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>表格不可換行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProductManagement</t>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ManageReservation</t>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>備註</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PGManagement</t>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DesignerManagement</t>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CouponPointManagement</t>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>V</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>V</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DesignerShiftManagement</t>
-  </si>
-  <si>
-    <t>Report</t>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MyCoupons</t>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新聞增加連結功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;a class="dropdown-item" asp-page="/about"&gt;&lt;i class="far fa-address-card nav-icon icon-width"&gt;&lt;/i&gt; 關於我們&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>&lt;a class="dropdown-item" asp-page="/Product"&gt;&lt;i class="fab fa-instagram nav-icon icon-width"&gt;&lt;/i&gt; 作品集&lt;/a&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;a class="dropdown-item" asp-page="/MakeReservation"&gt;&lt;i class="fas fa-clipboard-list nav-icon icon-width"&gt;&lt;/i&gt; 所有課程&amp;服務&lt;/a&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;a class="dropdown-item" asp-page="/contact"&gt;&lt;i class="far fa-comment-dots nav-icon icon-width"&gt;&lt;/i&gt; 聯絡我們&lt;/a&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目前mssql已經轉到docker裡面了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>現在還連不上網站</t>
+    <t>Line官方帳號訊息服務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用於發送驗證訊息與訊息服務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設為0則預約後不可取消</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客戶評分系統</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -895,7 +955,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -917,6 +977,15 @@
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -952,12 +1021,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -965,9 +1037,13 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2098,372 +2174,372 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B1" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D1" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="E1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1" t="s">
         <v>216</v>
       </c>
-      <c r="F1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J1" t="s">
         <v>225</v>
       </c>
-      <c r="H1" t="s">
-        <v>229</v>
-      </c>
-      <c r="I1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J1" t="s">
-        <v>238</v>
-      </c>
       <c r="K1" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="L1" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" t="s">
         <v>188</v>
       </c>
-      <c r="B2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C2" t="s">
-        <v>201</v>
-      </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="E2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H2" t="s">
         <v>217</v>
       </c>
-      <c r="F2" t="s">
-        <v>222</v>
-      </c>
-      <c r="G2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H2" t="s">
-        <v>230</v>
-      </c>
       <c r="I2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="J2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="K2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="L2" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D3" t="s">
         <v>197</v>
       </c>
-      <c r="C3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D3" t="s">
-        <v>210</v>
-      </c>
       <c r="E3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="F3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="G3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="H3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I3" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="J3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="K3" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="L3" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" t="s">
         <v>190</v>
       </c>
-      <c r="B4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" t="s">
-        <v>203</v>
-      </c>
       <c r="D4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="E4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="F4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="G4" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="H4" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I4" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="J4" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="K4" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="L4" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" t="s">
         <v>191</v>
       </c>
-      <c r="B5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" t="s">
-        <v>204</v>
-      </c>
       <c r="D5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="F5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="G5" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="H5" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I5" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="J5" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="K5" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="L5" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G6" t="s">
         <v>215</v>
       </c>
-      <c r="E6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F6" t="s">
-        <v>212</v>
-      </c>
-      <c r="G6" t="s">
-        <v>228</v>
-      </c>
       <c r="H6" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I6" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="J6" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="K6" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="L6" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="B7" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="E7" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="F7" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="G7" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="H7" t="s">
+        <v>183</v>
+      </c>
+      <c r="I7" t="s">
+        <v>221</v>
+      </c>
+      <c r="J7" t="s">
         <v>196</v>
       </c>
-      <c r="I7" t="s">
-        <v>234</v>
-      </c>
-      <c r="J7" t="s">
-        <v>209</v>
-      </c>
       <c r="K7" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="L7" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="E8" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="F8" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G8" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="H8" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="I8" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="J8" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="L8" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" t="s">
         <v>197</v>
       </c>
-      <c r="C10" t="s">
-        <v>201</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
+        <v>196</v>
+      </c>
+      <c r="G10" t="s">
         <v>213</v>
       </c>
-      <c r="E10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F10" t="s">
-        <v>209</v>
-      </c>
-      <c r="G10" t="s">
-        <v>226</v>
-      </c>
       <c r="H10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I10" t="s">
+        <v>224</v>
+      </c>
+      <c r="J10" t="s">
         <v>196</v>
       </c>
-      <c r="I10" t="s">
-        <v>237</v>
-      </c>
-      <c r="J10" t="s">
-        <v>209</v>
-      </c>
       <c r="K10" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="B11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" t="s">
         <v>201</v>
       </c>
-      <c r="C11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D11" t="s">
-        <v>214</v>
-      </c>
       <c r="E11" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="F11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G11" t="s">
+        <v>215</v>
+      </c>
+      <c r="H11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I11" t="s">
         <v>223</v>
       </c>
-      <c r="G11" t="s">
-        <v>228</v>
-      </c>
-      <c r="H11" t="s">
-        <v>231</v>
-      </c>
-      <c r="I11" t="s">
-        <v>236</v>
-      </c>
       <c r="J11" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="K11" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2475,32 +2551,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -2511,7 +2567,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="132.5" customWidth="1"/>
@@ -2519,12 +2575,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2535,127 +2586,271 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" t="s">
         <v>170</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1" t="s">
         <v>171</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D11" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D13" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>250</v>
+      </c>
+      <c r="D14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>251</v>
+      </c>
+      <c r="D15" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>252</v>
+      </c>
+      <c r="D16" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>255</v>
+      </c>
+      <c r="B18" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>272</v>
+      </c>
+      <c r="C19" t="s">
+        <v>271</v>
+      </c>
+      <c r="D19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>274</v>
+      </c>
+      <c r="B20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" t="s">
+        <v>275</v>
+      </c>
+      <c r="D20" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>262</v>
+      </c>
+      <c r="B21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" t="s">
+        <v>275</v>
+      </c>
+      <c r="D21" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>168</v>
+      </c>
+      <c r="C22" t="s">
+        <v>275</v>
+      </c>
+      <c r="D22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" t="s">
+        <v>275</v>
+      </c>
+      <c r="D23" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>263</v>
+      </c>
+      <c r="B24" t="s">
+        <v>264</v>
+      </c>
+      <c r="D24" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>173</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C25" t="s">
+        <v>276</v>
+      </c>
+      <c r="D25" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" t="s">
-        <v>167</v>
-      </c>
-      <c r="C8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>176</v>
-      </c>
-      <c r="B11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B12" t="s">
-        <v>179</v>
-      </c>
-      <c r="C12" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13" t="s">
-        <v>181</v>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>256</v>
+      </c>
+      <c r="B26" t="s">
+        <v>253</v>
+      </c>
+      <c r="C26" t="s">
+        <v>277</v>
+      </c>
+      <c r="D26" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C18" r:id="rId1" display="官方帳號的id例如@1234567"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="261" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <pageSetup paperSize="261" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId2"/>
 </worksheet>
 </file>